--- a/projects/project-3/assignment/src/data/qudt-class-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/qudt-class-axioms.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b1</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b1</t>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Base Unit</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b2</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A Base Unit is a unit adopted by convention for a base quantity.</t>
+          <t>Base Unit</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#DeprecatedClass</t>
+          <t>A Base Unit is a unit adopted by convention for a base quantity.</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b2</t>
+          <t>http://www.w3.org/2002/07/owl#DeprecatedClass</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b3</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b3</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b4</t>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b4</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b5</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b5</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#ScienceAndEngineeringUnit</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b6</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Computing Unit</t>
+          <t>http://qudt.org/schema/qudt#ScienceAndEngineeringUnit</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b6</t>
+          <t>Computing Unit</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b8</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b7</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b7</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b8</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>A DerivedUnit is a type specification for units that are derived from other units.</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b9</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b9</t>
+          <t>A DerivedUnit is a type specification for units that are derived from other units.</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b10</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b10</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b11</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b12</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b14</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b11</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b13</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b16</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b16</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b13</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b12</t>
+          <t>This class is for all enumerated and/or coded values.  For example, it contains the dimension objects that are the basis elements in some abstract vector space associated with a quantity kind system. Another use is for the base dimensions for quantity systems. Each quantity kind system that defines a base set has a corresponding ordered enumeration whose elements are the dimension objects for the base quantity kinds. The order of the dimensions in the enumeration determines the canonical order of the basis elements in the corresponding abstract vector space.</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>This class is for all enumerated and/or coded values.  For example, it contains the dimension objects that are the basis elements in some abstract vector space associated with a quantity kind system. Another use is for the base dimensions for quantity systems. Each quantity kind system that defines a base set has a corresponding ordered enumeration whose elements are the dimension objects for the base quantity kinds. The order of the dimensions in the enumeration determines the canonical order of the basis elements in the corresponding abstract vector space.</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b14</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Enumerated Value</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b15</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b15</t>
+          <t>Enumerated Value</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b21</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b19</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>http://www.linkedmodel.org/schema/dtype#Enumeration</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b18</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>This class is for describing the enumerations themselves. Having an enumerated value is one concept.  Having a way to descrive the set of enumerated valies is a distinct need. An enumeration is a collection of enumeration elements. In some cases it is necesaary to refer to the enumeration as opposed to one of its values.</t>
+          <t>http://www.linkedmodel.org/schema/dtype#Enumeration</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b18</t>
+          <t>This class is for describing the enumerations themselves. Having an enumerated value is one concept.  Having a way to descrive the set of enumerated valies is a distinct need. An enumeration is a collection of enumeration elements. In some cases it is necesaary to refer to the enumeration as opposed to one of its values.</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Enumeration</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b22</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b17</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b20</t>
+          <t>Enumeration</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b17</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b22</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b21</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b19</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b20</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b23</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#ResourceUnit</t>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Financial Unit</t>
+          <t>http://qudt.org/schema/qudt#ResourceUnit</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Financial Unit</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b23</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b24</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b24</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>http://qudt.org/schema/qudt#ResourceUnit</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#ResourceUnit</t>
+          <t>Information Entropy Unit</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Information Entropy Unit</t>
+          <t>http://qudt.org/schema/qudt#LogarithmicUnit</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#LogarithmicUnit</t>
+          <t>http://qudt.org/schema/qudt#ComputingUnit</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#ComputingUnit</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#PhotometryUnit</t>
+          <t>Luminance Unit</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Luminance Unit</t>
+          <t>http://qudt.org/schema/qudt#PhotometryUnit</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b25</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b25</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b26</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b26</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b27</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b27</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>http://qudt.org/schema/qudt#FinancialUnit</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Rate Of Return Unit</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#FinancialUnit</t>
+          <t>Rate Of Return Unit</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#SIUnit</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b28</t>
         </is>
       </c>
     </row>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#SIDerivedUnit</t>
+          <t>http://qudt.org/schema/qudt#SIUnit</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#DeprecatedClass</t>
+          <t>http://qudt.org/schema/qudt#SIDerivedUnit</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>http://dbpedia.org/resource/Category:SI_base_units</t>
+          <t>http://www.w3.org/2002/07/owl#DeprecatedClass</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>All SI units are derived from the SI Base units</t>
+          <t>http://dbpedia.org/resource/Category:SI_base_units</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b28</t>
+          <t>All SI units are derived from the SI Base units</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b29</t>
+          <t>Science And Engineering Unit</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Science And Engineering Unit</t>
+          <t>http://qudt.org/schema/qudt#Unit</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#Unit</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b29</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10023,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b30</t>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b30</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b32</t>
+          <t>http://dbpedia.org/resource/Category:Systems_of_units</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>http://dbpedia.org/resource/Category:Systems_of_units</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b31</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b31</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b33</t>
         </is>
       </c>
     </row>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b33</t>
+          <t>A system of units is a set of units which are chosen as the reference scales for some set of quantity kinds together with the definitions of each unit. Units may be defined by experimental observation or by proportion to another unit not included in the system. If the unit system is explicitly associated with a quantity kind system, then the unit system must define at least one unit for each quantity kind.</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>A system of units is a set of units which are chosen as the reference scales for some set of quantity kinds together with the definitions of each unit. Units may be defined by experimental observation or by proportion to another unit not included in the system. If the unit system is explicitly associated with a quantity kind system, then the unit system must define at least one unit for each quantity kind.</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b32</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Thermal Conductivity Unit</t>
+          <t>http://qudt.org/schema/qudt#ThermodynamicsUnit</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>http://qudt.org/schema/qudt#ThermodynamicsUnit</t>
+          <t>Thermal Conductivity Unit</t>
         </is>
       </c>
     </row>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Thermodynamics Unit</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b34</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>http://dbpedia.org/resource/Category:Thermodynamics</t>
+          <t>Thermodynamics Unit</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b34</t>
+          <t>http://dbpedia.org/resource/Category:Thermodynamics</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b35</t>
+          <t>http://dbpedia.org/resource/Category:Units_of_measure</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>http://dbpedia.org/resource/Category:Units_of_measure</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b42</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b37</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b35</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b38</t>
+          <t>A unit of measure, or unit, is a particular quantity value that has been chosen as a scale for measuring other quantities the same kind (more generally of equivalent dimension). For example, the meter is a quantity of length that has been rigorously defined and standardized by the BIPM (International Board of Weights and Measures). Any measurement of the length can be expressed as a number multiplied by the unit meter. More formally, the value of a physical quantity Q with respect to a unit (U) is expressed as the scalar multiple of a real number (n) and U, as  Q = nU.</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b42</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b38</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b39</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b36</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>A unit of measure, or unit, is a particular quantity value that has been chosen as a scale for measuring other quantities the same kind (more generally of equivalent dimension). For example, the meter is a quantity of length that has been rigorously defined and standardized by the BIPM (International Board of Weights and Measures). Any measurement of the length can be expressed as a number multiplied by the unit meter. More formally, the value of a physical quantity Q with respect to a unit (U) is expressed as the scalar multiple of a real number (n) and U, as  Q = nU.</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b37</t>
         </is>
       </c>
     </row>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b36</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b41</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b41</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b40</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>n835600169f9d41e8ab549ffe8eb2c9d0b40</t>
+          <t>nbeac9fadb1b84326bd5a78b8f3e688e0b39</t>
         </is>
       </c>
     </row>
